--- a/naver-place-crawler/results_derma/동구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/동구_피부과.xlsx
@@ -624,10 +624,10 @@
         <v>1434</v>
       </c>
       <c r="Q2" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="R2" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -661,11 +661,7 @@
           <t>김의원</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>drkim3119@naver.com</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
@@ -849,7 +845,11 @@
           <t>주안참고운의원</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>kimo23k@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
@@ -939,7 +939,11 @@
           <t>고운의원</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>thegounclinic@naver.com</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
@@ -1029,7 +1033,11 @@
           <t>연세비뇨기과의원</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>urouno1@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1364,10 +1372,10 @@
         <v>771</v>
       </c>
       <c r="Q10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R10" t="n">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1497,7 +1505,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dana7577@naver.com</t>
+          <t>dasibom3378@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1589,7 +1597,11 @@
           <t>주안연세의원</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lan_j_97@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
@@ -1679,11 +1691,7 @@
           <t>장편한내과의원</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>asanjang0062@naver.com</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
@@ -1773,11 +1781,7 @@
           <t>이현우메디칼의원</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>incheondonggu@naver.com</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -1961,7 +1965,11 @@
           <t>연세열린내과의원</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sangsang_plus777@naver.com</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
@@ -3085,11 +3093,7 @@
           <t>김의원</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>drkim3119@naver.com</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
@@ -3139,13 +3143,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Q29" t="n">
         <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3179,11 +3183,7 @@
           <t>뉴송림성모의원</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>incheondonggu@naver.com</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3461,7 +3461,11 @@
           <t>황호연산부인과</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>hhsung12@naver.com</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
@@ -3927,11 +3931,7 @@
           <t>신한대 바울요양병원</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ddoga_official@naver.com</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -4115,11 +4115,7 @@
           <t>한나이비인후과의원</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>nexgen84@naver.com</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
@@ -4360,10 +4356,10 @@
         <v>144</v>
       </c>
       <c r="Q42" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R42" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4520,7 +4516,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4736,10 +4732,10 @@
         <v>661</v>
       </c>
       <c r="Q46" t="n">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="R46" t="n">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -5173,12 +5169,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5459,12 +5455,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5485,7 +5481,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -5623,7 +5619,11 @@
           <t>아레나한방병원</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>three_voice@naver.com</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>songdoarena@gmail.com</t>
@@ -6371,11 +6371,7 @@
           <t>명가한의원</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>gamjaung@naver.com</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6829,7 +6825,11 @@
           <t>영제한의원</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>meilian7@naver.com</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -6919,7 +6919,11 @@
           <t>행림한의원</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>haengrim00@naver.com</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
@@ -7011,7 +7015,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>choigojeep@naver.com</t>
+          <t>ykhkmc@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7197,7 +7201,11 @@
           <t>익수한의원</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>suwooya@naver.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_derma/동구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/동구_피부과.xlsx
@@ -1033,11 +1033,7 @@
           <t>연세비뇨기과의원</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>urouno1@naver.com</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
@@ -1221,11 +1217,7 @@
           <t>행복한가정의학과의원</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>noblewoman0307@naver.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
@@ -1597,11 +1589,7 @@
           <t>주안연세의원</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>lan_j_97@naver.com</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
@@ -1691,7 +1679,11 @@
           <t>장편한내과의원</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>asanjang0062@naver.com</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
@@ -1781,7 +1773,11 @@
           <t>이현우메디칼의원</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>incheondonggu@naver.com</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -3183,7 +3179,11 @@
           <t>뉴송림성모의원</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>incheondonggu@naver.com</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
@@ -3743,11 +3743,7 @@
           <t>봄소아청소년과의원</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>bbped@naver.com</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3931,7 +3927,11 @@
           <t>신한대 바울요양병원</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ddoga_official@naver.com</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
@@ -4115,7 +4115,11 @@
           <t>한나이비인후과의원</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>nexgen84@naver.com</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
@@ -4516,7 +4520,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5108,10 +5112,10 @@
         <v>4910</v>
       </c>
       <c r="Q50" t="n">
-        <v>4377</v>
+        <v>4379</v>
       </c>
       <c r="R50" t="n">
-        <v>9287</v>
+        <v>9289</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5169,12 +5173,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5338,11 +5342,7 @@
           <t>icmc_or_kr@naver.com</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>csc@kihoilbo.co.kr</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>032-580-6000</t>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5382,7 +5382,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -5619,11 +5619,7 @@
           <t>아레나한방병원</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>three_voice@naver.com</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>songdoarena@gmail.com</t>
@@ -5905,7 +5901,11 @@
           <t>신농씨한의원</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>shinnong71@naver.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
@@ -6277,11 +6277,7 @@
           <t>화수한의원</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>shinppong@naver.com</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6371,7 +6367,11 @@
           <t>명가한의원</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gamjaung@naver.com</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6645,7 +6645,11 @@
           <t>송선당한의원</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>book_go@naver.com</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
@@ -6731,11 +6735,7 @@
           <t>뉴송림성모한의원</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>inimc0102@naver.com</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -7013,11 +7013,7 @@
           <t>동인천한의원</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>ykhkmc@naver.com</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_derma/동구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/동구_피부과.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메인의원 인천주안점</t>
+          <t>고운의원</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dudnf8970@naver.com</t>
+          <t>thegounclinic@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1334-8970</t>
+          <t>0507-1496-2806</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 716 204호, 205호, 206호</t>
+          <t>인천광역시 서구 거북로 98 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dudnf8970</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1434</v>
+        <v>74</v>
       </c>
       <c r="Q2" t="n">
-        <v>569</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>2003</v>
+        <v>78</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13106424</t>
+          <t>13240170</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13106424</t>
+          <t>https://m.place.naver.com/place/13240170</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -658,20 +658,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>김의원</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>고은미래의원 인천점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>go9037600@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>032-772-4346</t>
+          <t>032-579-7677</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 61-1 김의원,필라</t>
+          <t>인천광역시 서구 원적로 85 우신프라자 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>86</v>
+        <v>484</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>90</v>
+        <v>491</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13240833</t>
+          <t>13474824</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240833</t>
+          <t>https://m.place.naver.com/place/13474824</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>고은미래의원 인천점</t>
+          <t>메인의원 인천주안점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>go9037600@naver.com</t>
+          <t>dudnf8970@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>032-579-7677</t>
+          <t>0507-1334-8970</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 85 우신프라자 4층</t>
+          <t>인천광역시 미추홀구 미추홀대로 716 204호, 205호, 206호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dudnf8970</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -780,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -801,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>484</v>
+        <v>1433</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>578</v>
       </c>
       <c r="R4" t="n">
-        <v>491</v>
+        <v>2011</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13474824</t>
+          <t>13106424</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13474824</t>
+          <t>https://m.place.naver.com/place/13106424</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>주안참고운의원</t>
+          <t>김의원</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kimo23k@naver.com</t>
+          <t>drkim3119@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>032-862-7582</t>
+          <t>032-772-4346</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 제일로 38</t>
+          <t>인천광역시 중구 우현로 61-1 김의원,필라</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://chamgowoon.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="Q5" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>245</v>
+        <v>90</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>21361808</t>
+          <t>13240833</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21361808</t>
+          <t>https://m.place.naver.com/place/13240833</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -936,24 +940,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>고운의원</t>
+          <t>연세비뇨기과의원</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thegounclinic@naver.com</t>
+          <t>urouno1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1496-2806</t>
+          <t>032-766-6363</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 서구 거북로 98 3층</t>
+          <t>인천광역시 중구 우현로 86 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13240170</t>
+          <t>11715237</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240170</t>
+          <t>https://m.place.naver.com/place/11715237</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1030,25 +1034,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>연세비뇨기과의원</t>
+          <t>주안참고운의원</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>032-766-6363</t>
+          <t>032-862-7582</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 중구 우현로 86 2층</t>
+          <t>인천광역시 미추홀구 제일로 38</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://chamgowoon.com/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1058,7 +1062,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1083,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="R7" t="n">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11715237</t>
+          <t>21361808</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11715237</t>
+          <t>https://m.place.naver.com/place/21361808</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1120,24 +1124,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>큰나무의원</t>
+          <t>행복한가정의학과의원</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kunnamu7582@naver.com</t>
+          <t>noblewoman0307@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>032-571-0011</t>
+          <t>032-582-3824</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로151번길 11 가좌홈플러스 2층</t>
+          <t>인천광역시 서구 고래울로 4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1177,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>861</v>
+        <v>355</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>864</v>
+        <v>357</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,52 +1196,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>13240050</t>
+          <t>1965402967</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240050</t>
+          <t>https://m.place.naver.com/place/1965402967</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>가정의학과</t>
+          <t>내과</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>행복한가정의학과의원</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>연세열린내과의원</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sangsang_plus777@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>032-582-3824</t>
+          <t>0507-1352-6091</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 서구 고래울로 4</t>
+          <t>인천광역시 서구 가정로 201-1 두일빌딩 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://yonseimed.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1247,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1267,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>355</v>
+        <v>1974</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>357</v>
+        <v>1984</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1282,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1965402967</t>
+          <t>13240187</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965402967</t>
+          <t>https://m.place.naver.com/place/13240187</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1304,44 +1312,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>서해사랑내과의원</t>
+          <t>주안연세의원</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>seohaemedi@naver.com</t>
+          <t>lan_j_97@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>032-891-7575</t>
+          <t>032-874-0874</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 아암대로 15 아이클래스 3층</t>
+          <t>인천광역시 미추홀구 석정로423번길 3 라이온스빌딩</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://sarangmed.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1361,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>771</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>936</v>
+        <v>8</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1376,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>19575139</t>
+          <t>37912553</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19575139</t>
+          <t>https://m.place.naver.com/place/37912553</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1398,29 +1406,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한사랑내과의원</t>
+          <t>이현우메디칼의원</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jjj2823@naver.com</t>
+          <t>incheondonggu@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>032-865-1171</t>
+          <t>032-773-7227</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 수봉로 22-1 새마을금고 5층</t>
+          <t>인천광역시 동구 화도진로 137</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.oneluvclinic.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1430,7 +1438,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1451,17 +1459,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>528</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1470,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13241140</t>
+          <t>13240870</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241140</t>
+          <t>https://m.place.naver.com/place/13240870</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1492,24 +1500,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>동인천내과의원</t>
+          <t>행복한내과의원</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dasibom3378@naver.com</t>
+          <t>digerate@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1470-5676</t>
+          <t>032-863-3338</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 1 송현프라자</t>
+          <t>인천광역시 미추홀구 한나루로 591</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1549,13 +1557,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>579</v>
+        <v>386</v>
       </c>
       <c r="Q12" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="R12" t="n">
-        <v>635</v>
+        <v>400</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1564,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>31699925</t>
+          <t>11870875</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31699925</t>
+          <t>https://m.place.naver.com/place/11870875</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1586,25 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>주안연세의원</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>한사랑내과의원</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jjj2823@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>032-874-0874</t>
+          <t>032-865-1171</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로423번길 3 라이온스빌딩</t>
+          <t>인천광역시 미추홀구 수봉로 22-1 새마을금고 5층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.oneluvclinic.com/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1614,7 +1626,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1635,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>529</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>613</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1654,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>37912553</t>
+          <t>13241140</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37912553</t>
+          <t>https://m.place.naver.com/place/13241140</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1676,39 +1688,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>장편한내과의원</t>
+          <t>동인천내과의원</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>asanjang0062@naver.com</t>
+          <t>jangsaero_im@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>032-874-4004</t>
+          <t>0507-1470-5676</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 3층</t>
+          <t>인천광역시 동구 송현로 1 송현프라자</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://jangcomfort.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1733,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>504</v>
+        <v>580</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="R14" t="n">
-        <v>507</v>
+        <v>634</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1748,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1224558403</t>
+          <t>31699925</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224558403</t>
+          <t>https://m.place.naver.com/place/31699925</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1770,44 +1782,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>이현우메디칼의원</t>
+          <t>연세예스내과의원</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>incheondonggu@naver.com</t>
+          <t>yesclinic_juan@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>032-773-7227</t>
+          <t>0507-1412-6500</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 137</t>
+          <t>인천광역시 미추홀구 경인로 347 국제빌딩 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://yonseiyesclinic-mo4.imweb.me</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1823,17 +1835,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>120</v>
+        <v>457</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="R15" t="n">
-        <v>123</v>
+        <v>687</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1842,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13240870</t>
+          <t>1108374136</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240870</t>
+          <t>https://m.place.naver.com/place/1108374136</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1864,39 +1876,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>연세성모의원</t>
+          <t>장편한내과의원</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>happysofa_net@naver.com</t>
+          <t>asanjang0062@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>032-772-0266</t>
+          <t>032-874-4004</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 183 2층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 3층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://jangcomfort.com</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1921,13 +1933,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>228</v>
+        <v>505</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>228</v>
+        <v>508</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1936,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13240828</t>
+          <t>1224558403</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240828</t>
+          <t>https://m.place.naver.com/place/1224558403</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1958,34 +1970,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>연세열린내과의원</t>
+          <t>비타민내과의원</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sangsang_plus777@naver.com</t>
+          <t>accyto@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1352-6091</t>
+          <t>0507-1477-7012</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 201-1 두일빌딩 3층</t>
+          <t>인천광역시 동구 화도진로 109 204호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://yonseimed.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1995,7 +2007,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2015,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1985</v>
+        <v>349</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1995</v>
+        <v>350</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2030,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13240187</t>
+          <t>13240862</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240187</t>
+          <t>https://m.place.naver.com/place/13240862</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2052,34 +2064,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>주안속튼튼내과의원</t>
+          <t>연세성모의원</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sokteunteunim@naver.com</t>
+          <t>happysofa_net@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>032-710-0877</t>
+          <t>032-772-0266</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 391 3층</t>
+          <t>인천광역시 동구 화도진로 183 2층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://juansok.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2089,7 +2101,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2105,17 +2117,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>664</v>
+        <v>228</v>
       </c>
       <c r="Q18" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>937</v>
+        <v>228</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2124,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1303935179</t>
+          <t>13240828</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303935179</t>
+          <t>https://m.place.naver.com/place/13240828</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2146,24 +2158,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>우리내과의원소아과</t>
+          <t>인천제일의원</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>goodfl@naver.com</t>
+          <t>kimhb9189@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>032-777-3601</t>
+          <t>032-883-0380</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 93-1</t>
+          <t>인천광역시 미추홀구 경인로 32 인천제일의원</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2203,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>147</v>
+        <v>507</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>149</v>
+        <v>511</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2230,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>10977429</t>
+          <t>13241338</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/10977429</t>
+          <t>https://m.place.naver.com/place/13241338</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2252,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>연세예스내과의원</t>
+          <t>주안속튼튼내과의원</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yesclinic_juan@naver.com</t>
+          <t>sokteunteunim@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1412-6500</t>
+          <t>032-710-0877</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 347 국제빌딩 2층</t>
+          <t>인천광역시 미추홀구 석정로 391 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://yonseiyesclinic-mo4.imweb.me</t>
+          <t>http://juansok.co.kr/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2272,7 +2284,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2297,13 +2309,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>454</v>
+        <v>669</v>
       </c>
       <c r="Q20" t="n">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="R20" t="n">
-        <v>681</v>
+        <v>942</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1108374136</t>
+          <t>1303935179</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1108374136</t>
+          <t>https://m.place.naver.com/place/1303935179</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2334,24 +2346,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비타민내과의원</t>
+          <t>우리내과의원소아과</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>accyto@naver.com</t>
+          <t>goodfl@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1477-7012</t>
+          <t>032-777-3601</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 109 204호</t>
+          <t>인천광역시 동구 송림로 93-1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2391,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>349</v>
+        <v>136</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>350</v>
+        <v>138</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,56 +2418,56 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>13240862</t>
+          <t>10977429</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240862</t>
+          <t>https://m.place.naver.com/place/10977429</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대장,항문과</t>
+          <t>내과</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>이레외과의원</t>
+          <t>서해사랑내과의원</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>icyejihang@naver.com</t>
+          <t>seohaemedi@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>032-891-7172</t>
+          <t>032-891-7575</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 271 DH메디컬 5층 501~504호</t>
+          <t>인천광역시 미추홀구 아암대로 15 아이클래스 3층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/icyejihang</t>
+          <t>http://sarangmed.co.kr/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2485,13 +2497,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>396</v>
+        <v>773</v>
       </c>
       <c r="Q22" t="n">
-        <v>656</v>
+        <v>170</v>
       </c>
       <c r="R22" t="n">
-        <v>1052</v>
+        <v>943</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2500,51 +2512,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>12833522</t>
+          <t>19575139</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12833522</t>
+          <t>https://m.place.naver.com/place/19575139</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>대장,항문과</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>화수성심의원</t>
+          <t>이레외과의원</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>meschool24@naver.com</t>
+          <t>icyejihang@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>032-763-2017</t>
+          <t>032-891-7172</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 43 범성빌딩 2층</t>
+          <t>인천광역시 미추홀구 석정로 271 DH메디컬 5층 501~504호</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/icyejihang</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2554,12 +2566,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2579,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>191</v>
+        <v>395</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="R23" t="n">
-        <v>191</v>
+        <v>1197</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2594,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11858072</t>
+          <t>12833522</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11858072</t>
+          <t>https://m.place.naver.com/place/12833522</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2616,24 +2628,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>미스토리의원</t>
+          <t>김의원</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cherry3559@naver.com</t>
+          <t>drkim3119@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>032-582-2452</t>
+          <t>032-766-8384</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 서구 옻우물로 3</t>
+          <t>인천광역시 동구 송림로 83</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2673,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>19518705</t>
+          <t>13240822</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19518705</t>
+          <t>https://m.place.naver.com/place/13240822</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>동부제일의원</t>
+          <t>척척의원</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>congressional077@naver.com</t>
+          <t>chukchuk88@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>032-761-3171</t>
+          <t>032-777-3512</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화수로 18 동부아파트 상가동</t>
+          <t>인천광역시 동구 송미로 7 3층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/chukchuk88</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2742,12 +2754,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2767,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R25" t="n">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>19518715</t>
+          <t>1203082349</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19518715</t>
+          <t>https://m.place.naver.com/place/1203082349</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2804,24 +2816,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>연세도레미소아청소년과의원</t>
+          <t>뉴송림성모의원</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nester99@naver.com</t>
+          <t>incheondonggu@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>032-777-0119</t>
+          <t>032-773-7570</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 47 2층</t>
+          <t>인천광역시 동구 송림로 84 2층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2861,13 +2873,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>255</v>
+        <v>70</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>255</v>
+        <v>70</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1266018707</t>
+          <t>1699418867</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266018707</t>
+          <t>https://m.place.naver.com/place/1699418867</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2898,39 +2910,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>현대의원</t>
+          <t>동부제일의원</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>knk05051@naver.com</t>
+          <t>congressional077@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>032-764-9090</t>
+          <t>032-761-3171</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 80 송림센트럴타워 2층 현대의원</t>
+          <t>인천광역시 동구 화수로 18 동부아파트 상가동</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcxjExhn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2946,7 +2958,7 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2955,13 +2967,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>72</v>
+        <v>137</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1990702614</t>
+          <t>19518715</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1990702614</t>
+          <t>https://m.place.naver.com/place/19518715</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2992,29 +3004,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>척척의원</t>
+          <t>연세도레미소아청소년과의원</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>chukchuk88@naver.com</t>
+          <t>ina2248@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>032-777-3512</t>
+          <t>032-777-0119</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송미로 7 3층</t>
+          <t>인천광역시 동구 송현로 47 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/chukchuk88</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3024,12 +3036,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3049,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1203082349</t>
+          <t>1266018707</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1203082349</t>
+          <t>https://m.place.naver.com/place/1266018707</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3086,20 +3098,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>김의원</t>
+          <t>화수성심의원</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>032-766-8384</t>
+          <t>032-763-2017</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 83</t>
+          <t>인천광역시 동구 화수로 43 범성빌딩 2층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3139,13 +3151,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3154,17 +3166,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13240822</t>
+          <t>11858072</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240822</t>
+          <t>https://m.place.naver.com/place/11858072</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3176,39 +3188,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>뉴송림성모의원</t>
+          <t>현대의원</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>incheondonggu@naver.com</t>
+          <t>knk05051@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>032-773-7570</t>
+          <t>032-764-9090</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 84 2층</t>
+          <t>인천광역시 동구 송림로 80 송림센트럴타워 2층 현대의원</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xcxjExhn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3224,7 +3236,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3233,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3248,46 +3260,46 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1699418867</t>
+          <t>1990702614</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1699418867</t>
+          <t>https://m.place.naver.com/place/1990702614</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>비뇨의학과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>미르비뇨기과의원</t>
+          <t>미스토리의원</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>siwznwlkoj81236@naver.com</t>
+          <t>cherry3559@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>032-765-9114</t>
+          <t>032-582-2452</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 96 송림메디칼빌딩 301호</t>
+          <t>인천광역시 서구 옻우물로 3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3327,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>354</v>
+        <v>190</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>354</v>
+        <v>197</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3342,17 +3354,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>19523554</t>
+          <t>19518705</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19523554</t>
+          <t>https://m.place.naver.com/place/19518705</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3421,14 +3433,14 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>786</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
         <v>788</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>789</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>X</t>
@@ -3446,36 +3458,36 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>산부인과</t>
+          <t>비뇨의학과</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>황호연산부인과</t>
+          <t>미르비뇨기과의원</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>hhsung12@naver.com</t>
+          <t>siwznwlkoj81236@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>032-761-3222</t>
+          <t>032-765-9114</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 188</t>
+          <t>인천광역시 동구 송림로 96 송림메디칼빌딩 301호</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3515,13 +3527,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>9</v>
+        <v>354</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>9</v>
+        <v>354</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,46 +3542,46 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1233536125</t>
+          <t>19523554</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1233536125</t>
+          <t>https://m.place.naver.com/place/19523554</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>성형외과</t>
+          <t>산부인과</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>본의원</t>
+          <t>황호연산부인과</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>dreamjoonskh@naver.com</t>
+          <t>hhsung12@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-873-6666</t>
+          <t>032-761-3222</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 731</t>
+          <t>인천광역시 동구 샛골로 188</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3609,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3636,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>13241224</t>
+          <t>1233536125</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241224</t>
+          <t>https://m.place.naver.com/place/1233536125</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3740,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3755,11 @@
           <t>봄소아청소년과의원</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bbped@naver.com</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
@@ -3818,7 +3834,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3830,34 +3846,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>인천사랑요양병원</t>
+          <t>도화요양병원</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>incheonheart@naver.com</t>
+          <t>dohwahosp@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>032-421-0503</t>
+          <t>032-865-0033</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 400</t>
+          <t>인천광역시 미추홀구 경인로 302</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/incheonheart</t>
+          <t>http://www.dohwahospital.com/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3867,7 +3883,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3887,13 +3903,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="Q37" t="n">
-        <v>319</v>
+        <v>120</v>
       </c>
       <c r="R37" t="n">
-        <v>490</v>
+        <v>178</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,17 +3918,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37885832</t>
+          <t>13300496</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37885832</t>
+          <t>https://m.place.naver.com/place/13300496</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3924,34 +3940,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>신한대 바울요양병원</t>
+          <t>인천사랑요양병원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ddoga_official@naver.com</t>
+          <t>incheonheart@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>032-223-7000</t>
+          <t>032-421-0503</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 107 지2층~8층</t>
+          <t>인천광역시 미추홀구 경인로 400</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://www.신한대바울요양병원.com/</t>
+          <t>https://blog.naver.com/incheonheart</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3961,7 +3977,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3981,13 +3997,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>172</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>325</v>
       </c>
       <c r="R38" t="n">
-        <v>11</v>
+        <v>497</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,61 +4012,61 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1906967285</t>
+          <t>37885832</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1906967285</t>
+          <t>https://m.place.naver.com/place/37885832</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>요양병원</t>
+          <t>이비인후과</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>도화요양병원</t>
+          <t>송림이비인후과의원</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>dohwahosp@naver.com</t>
+          <t>medigate_official@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>032-865-0033</t>
+          <t>032-772-7500</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 302</t>
+          <t>인천광역시 동구 송림로 96 송림메디컬빌딩 3층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.dohwahospital.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4075,13 +4091,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>58</v>
+        <v>482</v>
       </c>
       <c r="Q39" t="n">
-        <v>117</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>175</v>
+        <v>485</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4106,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>13300496</t>
+          <t>11701457</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13300496</t>
+          <t>https://m.place.naver.com/place/11701457</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4169,13 +4185,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q40" t="n">
         <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4194,46 +4210,46 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>이비인후과</t>
+          <t>재활의학과</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>송림이비인후과의원</t>
+          <t>퍼스트병원</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>medigate_official@naver.com</t>
+          <t>physical9800@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>032-772-7500</t>
+          <t>032-888-9800</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 96 송림메디컬빌딩 3층</t>
+          <t>인천광역시 중구 서해대로 492 퍼스트병원</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://퍼스트병원.com</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4243,7 +4259,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4263,13 +4279,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>482</v>
+        <v>147</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>193</v>
       </c>
       <c r="R41" t="n">
-        <v>485</v>
+        <v>340</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4278,51 +4294,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11701457</t>
+          <t>1193797435</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11701457</t>
+          <t>https://m.place.naver.com/place/1193797435</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>재활의학과</t>
+          <t>정신건강의학과</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>퍼스트병원</t>
+          <t>모아병원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>physical9800@naver.com</t>
+          <t>fromthemoontoyou@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>032-888-9800</t>
+          <t>032-508-7513</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>인천광역시 중구 서해대로 492 퍼스트병원</t>
+          <t>인천광역시 미추홀구 미추홀대로 730 1층 일부, 2층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://퍼스트병원.com</t>
+          <t>http://www.모아병원.com</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4332,12 +4348,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4357,13 +4373,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>144</v>
+        <v>228</v>
       </c>
       <c r="Q42" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>329</v>
+        <v>229</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4388,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1193797435</t>
+          <t>12030750</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1193797435</t>
+          <t>https://m.place.naver.com/place/12030750</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4397,11 +4413,7 @@
           <t>인천우리병원</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>cheongdamwrd@naver.com</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -4454,10 +4466,10 @@
         <v>10</v>
       </c>
       <c r="Q43" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="R43" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4476,41 +4488,41 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>정신건강의학과</t>
+          <t>정형외과</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>모아병원</t>
+          <t>척척본의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>yy2082@naver.com</t>
+          <t>chucchucbone@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>032-508-7513</t>
+          <t>0507-1416-8878</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 730 1층 일부, 2층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 14 401호, 402호, 403호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.모아병원.com</t>
+          <t>https://chukchukbone.kr/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4520,12 +4532,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4541,17 +4553,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>229</v>
+        <v>919</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>386</v>
       </c>
       <c r="R44" t="n">
-        <v>230</v>
+        <v>1305</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4560,17 +4572,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>12030750</t>
+          <t>1272730632</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12030750</t>
+          <t>https://m.place.naver.com/place/1272730632</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4582,34 +4594,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>도화신경외과의원</t>
+          <t>저스트병원</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>dsns2016@naver.com</t>
+          <t>justhospital@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>032-888-4975</t>
+          <t>1544-1554</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 271 DH메디컬빌딩 4층 도화신경외과</t>
+          <t>인천광역시 미추홀구 석정로 21 저스트병원 4층 - 7층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dsns2016</t>
+          <t>http://www.hospitaljust.com</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4630,22 +4642,22 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>698</v>
+        <v>4909</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>4451</v>
       </c>
       <c r="R45" t="n">
-        <v>713</v>
+        <v>9360</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4654,17 +4666,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>37610933</t>
+          <t>1166592955</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37610933</t>
+          <t>https://m.place.naver.com/place/1166592955</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4676,29 +4688,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>도화본365의원</t>
+          <t>도화신경외과의원</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mjbhk84707@naver.com</t>
+          <t>dsns2016@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1422-7544</t>
+          <t>032-888-4975</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 5 앨리웨이 라이프동 204동 2층</t>
+          <t>인천광역시 미추홀구 석정로 271 DH메디컬빌딩 4층 도화신경외과</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.dhb365.co.kr</t>
+          <t>https://blog.naver.com/dsns2016</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4713,7 +4725,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4733,13 +4745,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="Q46" t="n">
-        <v>1058</v>
+        <v>16</v>
       </c>
       <c r="R46" t="n">
-        <v>1719</v>
+        <v>717</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4760,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1453258715</t>
+          <t>37610933</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1453258715</t>
+          <t>https://m.place.naver.com/place/37610933</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4770,29 +4782,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>마디정형외과의원</t>
+          <t>모세정형외과의원</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>madios365@naver.com</t>
+          <t>lyxee7@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1419-8275</t>
+          <t>032-764-1700</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>인천광역시 동구 수문통로 7</t>
+          <t>인천광역시 동구 송림로 102-1 모세정형외과의원</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/madios365</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4802,12 +4814,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4827,13 +4839,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1363</v>
+        <v>341</v>
       </c>
       <c r="Q47" t="n">
-        <v>1457</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2820</v>
+        <v>341</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4854,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>36271488</t>
+          <t>12765042</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36271488</t>
+          <t>https://m.place.naver.com/place/12765042</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4864,29 +4876,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>모세정형외과의원</t>
+          <t>마디정형외과의원</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kahyang@naver.com</t>
+          <t>madios365@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>032-764-1700</t>
+          <t>0507-1419-8275</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 102-1 모세정형외과의원</t>
+          <t>인천광역시 동구 수문통로 7</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/madios365</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4896,12 +4908,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4921,13 +4933,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>341</v>
+        <v>1363</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1467</v>
       </c>
       <c r="R48" t="n">
-        <v>341</v>
+        <v>2830</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4948,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>12765042</t>
+          <t>36271488</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12765042</t>
+          <t>https://m.place.naver.com/place/36271488</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4958,44 +4970,44 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>척척본의원</t>
+          <t>도화본365의원</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>chucchucbone@naver.com</t>
+          <t>mjbhk84707@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1416-8878</t>
+          <t>0507-1422-7544</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 14 401호, 402호, 403호</t>
+          <t>인천광역시 미추홀구 숙골로87번길 5 앨리웨이 라이프동 204동 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://chukchukbone.kr/</t>
+          <t>https://www.dhb365.co.kr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5011,17 +5023,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>906</v>
+        <v>674</v>
       </c>
       <c r="Q49" t="n">
-        <v>386</v>
+        <v>1093</v>
       </c>
       <c r="R49" t="n">
-        <v>1292</v>
+        <v>1767</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,56 +5042,56 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1272730632</t>
+          <t>1453258715</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1272730632</t>
+          <t>https://m.place.naver.com/place/1453258715</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>정형외과</t>
+          <t>종합병원</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>저스트병원</t>
+          <t>나은병원</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>justhospital@naver.com</t>
+          <t>naeun4119@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1544-1554</t>
+          <t>1661-0099</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 석정로 21 저스트병원 4층 - 7층</t>
+          <t>인천광역시 서구 원적로 23</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://www.hospitaljust.com</t>
+          <t>http://www.luga.co.kr/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5109,13 +5121,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4910</v>
+        <v>1684</v>
       </c>
       <c r="Q50" t="n">
-        <v>4379</v>
+        <v>915</v>
       </c>
       <c r="R50" t="n">
-        <v>9289</v>
+        <v>2599</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5136,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1166592955</t>
+          <t>11573592</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166592955</t>
+          <t>https://m.place.naver.com/place/11573592</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5146,39 +5158,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>나은병원</t>
+          <t>현대유비스병원</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>naeun4119@naver.com</t>
+          <t>hduvislee@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1661-0099</t>
+          <t>032-888-7575</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 23</t>
+          <t>인천광역시 미추홀구 독배로 503 현대유비스병원</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://www.luga.co.kr/</t>
+          <t>http://www.uvishospital.co.kr/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5203,13 +5215,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1690</v>
+        <v>1232</v>
       </c>
       <c r="Q51" t="n">
-        <v>915</v>
+        <v>791</v>
       </c>
       <c r="R51" t="n">
-        <v>2605</v>
+        <v>2023</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5230,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>11573592</t>
+          <t>12020177</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11573592</t>
+          <t>https://m.place.naver.com/place/12020177</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5240,44 +5252,44 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>현대유비스병원</t>
+          <t>인하대병원</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>hduvislee@naver.com</t>
+          <t>inhamedical@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>032-888-7575</t>
+          <t>032-890-2114</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 503 현대유비스병원</t>
+          <t>인천광역시 중구 인항로 27</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>http://www.uvishospital.co.kr/</t>
+          <t>http://www.inha.com/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5297,13 +5309,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1230</v>
+        <v>2071</v>
       </c>
       <c r="Q52" t="n">
-        <v>787</v>
+        <v>557</v>
       </c>
       <c r="R52" t="n">
-        <v>2017</v>
+        <v>2628</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5324,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>12020177</t>
+          <t>11686918</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12020177</t>
+          <t>https://m.place.naver.com/place/11686918</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5354,11 @@
           <t>icmc_or_kr@naver.com</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>goodluck@yna.co.kr</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>032-580-6000</t>
@@ -5361,7 +5377,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5371,7 +5387,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5382,7 +5398,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5394,10 +5410,10 @@
         <v>369</v>
       </c>
       <c r="Q53" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R53" t="n">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5416,51 +5432,51 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>종합병원</t>
+          <t>한방병원</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>인하대병원</t>
+          <t>성모사랑한방병원</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>inhamedical@naver.com</t>
+          <t>osu1125@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>032-890-2114</t>
+          <t>032-575-3200</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>인천광역시 중구 인항로 27</t>
+          <t>인천광역시 서구 길주로 91 성모사랑한방병원</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>http://www.inha.com/</t>
+          <t>https://www.sungmosarang365.com</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5476,22 +5492,22 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2070</v>
+        <v>391</v>
       </c>
       <c r="Q54" t="n">
-        <v>552</v>
+        <v>675</v>
       </c>
       <c r="R54" t="n">
-        <v>2622</v>
+        <v>1066</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5516,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>11686918</t>
+          <t>1497747553</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11686918</t>
+          <t>https://m.place.naver.com/place/1497747553</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5522,39 +5538,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>성모사랑한방병원</t>
+          <t>신세계한방병원</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>osu1125@naver.com</t>
+          <t>sinsegyehospital@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>032-575-3200</t>
+          <t>032-766-3737</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>인천광역시 서구 길주로 91 성모사랑한방병원</t>
+          <t>인천광역시 중구 서해대로 463 1-4층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.sungmosarang365.com</t>
+          <t>https://ssghospital.kr/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5575,17 +5591,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>385</v>
+        <v>41</v>
       </c>
       <c r="Q55" t="n">
-        <v>657</v>
+        <v>42</v>
       </c>
       <c r="R55" t="n">
-        <v>1042</v>
+        <v>83</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,17 +5610,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1497747553</t>
+          <t>1091606431</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497747553</t>
+          <t>https://m.place.naver.com/place/1091606431</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5616,29 +5632,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>아레나한방병원</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>songdoarena@gmail.com</t>
-        </is>
-      </c>
+          <t>참바른한방병원</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>drcham@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>032-465-1001</t>
+          <t>032-441-1722</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 주안로 116</t>
+          <t>인천광역시 미추홀구 미추홀대로 702 지하1, 1, 5, 6층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>http://arena-koreanmedicine.com/default/</t>
+          <t>http://chambarunhospital.co.kr/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5648,7 +5664,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5669,17 +5685,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="Q56" t="n">
-        <v>353</v>
+        <v>16</v>
       </c>
       <c r="R56" t="n">
-        <v>562</v>
+        <v>176</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,17 +5704,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1011297503</t>
+          <t>11676606</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1011297503</t>
+          <t>https://m.place.naver.com/place/11676606</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5710,44 +5726,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>신세계한방병원</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>sinsegyehospital@naver.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>아레나한방병원</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>songdoarena@gmail.com</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>032-766-3737</t>
+          <t>032-465-1001</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>인천광역시 중구 서해대로 463 1-4층</t>
+          <t>인천광역시 미추홀구 주안로 116</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://ssghospital.kr/</t>
+          <t>http://arena-koreanmedicine.com/default/</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5767,13 +5783,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>41</v>
+        <v>217</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>363</v>
       </c>
       <c r="R57" t="n">
-        <v>83</v>
+        <v>580</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5798,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1091606431</t>
+          <t>1011297503</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1091606431</t>
+          <t>https://m.place.naver.com/place/1011297503</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5804,34 +5820,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>연합한의원</t>
+          <t>송림한의원</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sywhani@naver.com</t>
+          <t>slhanmedi@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>032-574-1075</t>
+          <t>032-762-3025</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>인천광역시 서구 가정로 212</t>
+          <t>인천광역시 동구 송림로 96 503호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sywhani</t>
+          <t>https://sites.google.com/view/songlimhaniwon</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5861,13 +5877,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>668</v>
+        <v>207</v>
       </c>
       <c r="Q58" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>732</v>
+        <v>212</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,17 +5892,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>13240104</t>
+          <t>11687480</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240104</t>
+          <t>https://m.place.naver.com/place/11687480</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5898,24 +5914,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>신농씨한의원</t>
+          <t>송선당한의원</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>shinnong71@naver.com</t>
+          <t>book_go@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1364-3175</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 109 106호</t>
+          <t>인천광역시 동구 송현로11번길 4</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5955,13 +5967,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,17 +5982,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13240876</t>
+          <t>1945267627</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240876</t>
+          <t>https://m.place.naver.com/place/1945267627</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5992,34 +6004,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>이승진한의원</t>
+          <t>올바른한의원</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>lee_amc@naver.com</t>
+          <t>the1808@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>032-765-7522</t>
+          <t>032-887-1075</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>인천광역시 동구 샛골로 182</t>
+          <t>인천광역시 미추홀구 수봉로 22-1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://allbareun.net/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6049,13 +6061,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>71</v>
+        <v>246</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="R60" t="n">
-        <v>72</v>
+        <v>314</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6064,17 +6076,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>36476242</t>
+          <t>31004168</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36476242</t>
+          <t>https://m.place.naver.com/place/31004168</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6086,29 +6098,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>가좌고한의원</t>
+          <t>초록한의원</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>letsgo1103@naver.com</t>
+          <t>chorok9405@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1348-9397</t>
+          <t>032-777-1727</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 96 2층</t>
+          <t>인천광역시 동구 금곡로 34 1층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/letsgo1103</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6118,12 +6130,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6139,17 +6151,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>165</v>
+        <v>20</v>
       </c>
       <c r="Q61" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6158,17 +6170,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>2044964142</t>
+          <t>752229090</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044964142</t>
+          <t>https://m.place.naver.com/place/752229090</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6180,44 +6192,44 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>송림한의원</t>
+          <t>화수한의원</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>slhanmedi@naver.com</t>
+          <t>kyeongin_omc@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>032-762-3025</t>
+          <t>032-766-1075</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 96 503호</t>
+          <t>인천광역시 동구 운교로 6 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/songlimhaniwon</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6237,13 +6249,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6252,17 +6264,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>11687480</t>
+          <t>1668207974</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11687480</t>
+          <t>https://m.place.naver.com/place/1668207974</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6274,20 +6286,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>화수한의원</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>뉴송림성모한의원</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>qkql1313@naver.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>032-766-1075</t>
+          <t>032-773-7570</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>인천광역시 동구 운교로 6 1층</t>
+          <t>인천광역시 동구 송림로 84 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6327,13 +6343,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>159</v>
+        <v>8</v>
       </c>
       <c r="Q63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6358,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1668207974</t>
+          <t>1525190378</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1668207974</t>
+          <t>https://m.place.naver.com/place/1525190378</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6364,44 +6380,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>명가한의원</t>
+          <t>경인한의원</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gamjaung@naver.com</t>
+          <t>kyeongin_omc@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>0507-1358-5226</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 2 2층</t>
+          <t>인천광역시 동구 화도진로 63 경인한의원</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>http://명가한의원.com</t>
+          <t>https://blog.naver.com/kyeongin_omc</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6421,13 +6433,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2039</v>
+        <v>62</v>
       </c>
       <c r="Q64" t="n">
-        <v>447</v>
+        <v>90</v>
       </c>
       <c r="R64" t="n">
-        <v>2486</v>
+        <v>152</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6448,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1062899119</t>
+          <t>1637742901</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1062899119</t>
+          <t>https://m.place.naver.com/place/1637742901</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6458,34 +6470,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>동화한의원</t>
+          <t>동제당한의원</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>donghwahani@naver.com</t>
+          <t>dongjedang@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1348-1775</t>
+          <t>0507-1442-7733</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로 78 라이프쇼핑센터</t>
+          <t>인천광역시 동구 동산로 88 동제당한의원</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/donghwahani</t>
+          <t>https://www.dongjedang.com</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6495,7 +6507,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6515,13 +6527,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>380</v>
+        <v>62</v>
       </c>
       <c r="Q65" t="n">
-        <v>433</v>
+        <v>107</v>
       </c>
       <c r="R65" t="n">
-        <v>813</v>
+        <v>169</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6530,17 +6542,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>13240153</t>
+          <t>13240803</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240153</t>
+          <t>https://m.place.naver.com/place/13240803</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6552,25 +6564,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>경인한의원</t>
+          <t>바른정한의원</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kyeongin_omc@naver.com</t>
+          <t>khbaruenj00@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>032-868-7511</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 63 경인한의원</t>
+          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 204호 바른정한의원</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kyeongin_omc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6580,12 +6596,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6605,13 +6621,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>62</v>
+        <v>563</v>
       </c>
       <c r="Q66" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="R66" t="n">
-        <v>152</v>
+        <v>626</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6620,17 +6636,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1637742901</t>
+          <t>1418756412</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637742901</t>
+          <t>https://m.place.naver.com/place/1418756412</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6642,20 +6658,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>송선당한의원</t>
+          <t>영제한의원</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>book_go@naver.com</t>
+          <t>meilian7@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>032-882-2559</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로11번길 4</t>
+          <t>인천광역시 미추홀구 경인로 47-1 영제한의원</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6695,13 +6715,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R67" t="n">
-        <v>50</v>
+        <v>270</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6710,17 +6730,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1945267627</t>
+          <t>13241299</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945267627</t>
+          <t>https://m.place.naver.com/place/13241299</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6732,20 +6752,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>뉴송림성모한의원</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>주안한의원</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>jainhani77@naver.com</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>032-773-7570</t>
+          <t>032-872-3888</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송림로 84 2층</t>
+          <t>인천광역시 미추홀구 미추홀대로 725 광원빌딩 4층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6785,13 +6809,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>8</v>
+        <v>187</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>8</v>
+        <v>188</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6800,17 +6824,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1525190378</t>
+          <t>1465453554</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1525190378</t>
+          <t>https://m.place.naver.com/place/1465453554</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6822,24 +6846,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>영제한의원</t>
+          <t>익수한의원</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>meilian7@naver.com</t>
+          <t>suwooya@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>032-882-2559</t>
+          <t>032-763-7582</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 47-1 영제한의원</t>
+          <t>인천광역시 동구 화도진로 65</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6879,13 +6903,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>264</v>
+        <v>91</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>270</v>
+        <v>93</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6894,17 +6918,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>13241299</t>
+          <t>13240788</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13241299</t>
+          <t>https://m.place.naver.com/place/13240788</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6916,34 +6940,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>행림한의원</t>
+          <t>가좌고한의원</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>haengrim00@naver.com</t>
+          <t>letsgo1103@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1326-1076</t>
+          <t>0507-1348-9397</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 능해길 11</t>
+          <t>인천광역시 서구 원적로 96 2층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://thesoo.co/@haenglim</t>
+          <t>https://blog.naver.com/letsgo1103</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6953,7 +6977,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6969,17 +6993,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>589</v>
+        <v>173</v>
       </c>
       <c r="Q70" t="n">
-        <v>236</v>
+        <v>37</v>
       </c>
       <c r="R70" t="n">
-        <v>825</v>
+        <v>210</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6988,17 +7012,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>205176952</t>
+          <t>2044964142</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/205176952</t>
+          <t>https://m.place.naver.com/place/2044964142</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7010,20 +7034,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>동인천한의원</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>이승진한의원</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>lee_amc@naver.com</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>032-766-1070</t>
+          <t>032-765-7522</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 70 3층</t>
+          <t>인천광역시 동구 샛골로 182</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7063,13 +7091,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7078,17 +7106,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1039412632</t>
+          <t>36476242</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1039412632</t>
+          <t>https://m.place.naver.com/place/36476242</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7100,34 +7128,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>초록한의원</t>
+          <t>명가한의원</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>chorok9405@naver.com</t>
+          <t>gamjaung@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>032-777-1727</t>
+          <t>0507-1358-5226</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>인천광역시 동구 금곡로 34 1층</t>
+          <t>인천광역시 미추홀구 숙골로87번길 2 2층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://명가한의원.com</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7157,13 +7185,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>20</v>
+        <v>2047</v>
       </c>
       <c r="Q72" t="n">
-        <v>5</v>
+        <v>449</v>
       </c>
       <c r="R72" t="n">
-        <v>25</v>
+        <v>2496</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7172,17 +7200,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>752229090</t>
+          <t>1062899119</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/752229090</t>
+          <t>https://m.place.naver.com/place/1062899119</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7194,24 +7222,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>익수한의원</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>suwooya@naver.com</t>
-        </is>
-      </c>
+          <t>명인한의원</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>032-763-7582</t>
+          <t>032-777-6886</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>인천광역시 동구 화도진로 65</t>
+          <t>인천광역시 동구 송현로 38</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7251,13 +7275,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7266,17 +7290,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>13240788</t>
+          <t>13240878</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240788</t>
+          <t>https://m.place.naver.com/place/13240878</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7288,24 +7312,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>명인한의원</t>
+          <t>신농씨한의원</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>brightin5234@naver.com</t>
+          <t>shinnong71@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>032-777-6886</t>
+          <t>0507-1364-3175</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>인천광역시 동구 송현로 38</t>
+          <t>인천광역시 동구 화도진로 109 106호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7348,10 +7372,10 @@
         <v>61</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7360,17 +7384,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>13240878</t>
+          <t>13240876</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240878</t>
+          <t>https://m.place.naver.com/place/13240876</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7382,24 +7406,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>바른정한의원</t>
+          <t>동인천한의원</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>khbaruenj00@naver.com</t>
+          <t>wrmedical@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>032-868-7511</t>
+          <t>032-766-1070</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 204호 바른정한의원</t>
+          <t>인천광역시 동구 화도진로 70 3층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7439,13 +7463,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>562</v>
+        <v>17</v>
       </c>
       <c r="Q75" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>624</v>
+        <v>19</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7454,17 +7478,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1418756412</t>
+          <t>1039412632</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418756412</t>
+          <t>https://m.place.naver.com/place/1039412632</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7476,29 +7500,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>안산한의원</t>
+          <t>제물포한의원 서구점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ansan0110@naver.com</t>
+          <t>xavisnet@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>032-577-0110</t>
+          <t>032-582-8875</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>인천광역시 서구 원적로96번길 8 2층 안산한의원</t>
+          <t>인천광역시 서구 옻우물로 3 2층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansan0110</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7508,12 +7532,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7533,13 +7557,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>168</v>
+        <v>430</v>
       </c>
       <c r="Q76" t="n">
-        <v>384</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>552</v>
+        <v>433</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,17 +7572,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>13240149</t>
+          <t>1288745377</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13240149</t>
+          <t>https://m.place.naver.com/place/1288745377</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
